--- a/r5-ELGA-MOPED-256-Beispiele-für-maskierte-Ressourcen-erstellen/StructureDefinition-MOPEDEncounterSV.xlsx
+++ b/r5-ELGA-MOPED-256-Beispiele-für-maskierte-Ressourcen-erstellen/StructureDefinition-MOPEDEncounterSV.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T14:27:25+00:00</t>
+    <t>2024-11-11T10:32:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>
